--- a/बजेट माग estimate/नगर बजेट estimate/तल्लो नंग्लेद्वारे चिहानपाटी/devithaan.xlsx
+++ b/बजेट माग estimate/नगर बजेट estimate/तल्लो नंग्लेद्वारे चिहानपाटी/devithaan.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{284D0B99-7BD8-4D7E-9A0B-398B232E04F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D33159-4A5D-458E-887D-66CCC726AE21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
     <definedName name="description_781">#REF!</definedName>
     <definedName name="description_783">[1]Abstract!$B$301</definedName>
     <definedName name="description_784">[3]Abstract!$B$300</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">estimate!$A$8:$K$91</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">estimate!$A$1:$K$103</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">estimate!$1:$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="83">
   <si>
     <t>Government of Nepal</t>
   </si>
@@ -75,9 +75,6 @@
     <t>Detail Estimated Sheet</t>
   </si>
   <si>
-    <t>Location:- Shankharapur Municipality 9</t>
-  </si>
-  <si>
     <t>S.N.</t>
   </si>
   <si>
@@ -114,9 +111,6 @@
     <t>Sub-total</t>
   </si>
   <si>
-    <t>m3</t>
-  </si>
-  <si>
     <t>Information board (सुचना पाटि)</t>
   </si>
   <si>
@@ -129,9 +123,6 @@
     <t>Total</t>
   </si>
   <si>
-    <t xml:space="preserve">Date:                </t>
-  </si>
-  <si>
     <t>Budget allocated</t>
   </si>
   <si>
@@ -195,9 +186,6 @@
     <t>-VAT 13% for materials</t>
   </si>
   <si>
-    <t>Project:-देविथान निर्माण कार्य</t>
-  </si>
-  <si>
     <t>-MS square pipe of 3" * 3" of 3mm thickness for vertical post</t>
   </si>
   <si>
@@ -282,9 +270,6 @@
     <t>-for chihaan</t>
   </si>
   <si>
-    <t>m2</t>
-  </si>
-  <si>
     <t>-MS square pipe horizontal of 2" * 2" of 2mm thickness  for vertical post of railing</t>
   </si>
   <si>
@@ -292,6 +277,36 @@
   </si>
   <si>
     <t>-for railing</t>
+  </si>
+  <si>
+    <t>-High Density Polythene Pipe NS 40 pipe material PE 100, PN 16</t>
+  </si>
+  <si>
+    <t>-for watersupply</t>
+  </si>
+  <si>
+    <t>Weight (Kg/m)</t>
+  </si>
+  <si>
+    <t>Total weight (Kg)</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
+    <t>Date:2082/09/07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project:- तल्लो नाङ्गलेद्वारे चिहानपाटी </t>
+  </si>
+  <si>
+    <t>Location:- Shankharapur Municipality 1</t>
+  </si>
+  <si>
+    <t>-13% VAT for material</t>
+  </si>
+  <si>
+    <t>-13% VAT for brick</t>
   </si>
 </sst>
 </file>
@@ -302,7 +317,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -367,6 +382,7 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -374,44 +390,14 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <b/>
       <sz val="12"/>
-      <color rgb="FFFF0000"/>
       <name val="Preeti"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <sz val="12"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -495,7 +481,7 @@
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -581,64 +567,40 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -675,9 +637,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1205,7 +1164,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S98"/>
+  <dimension ref="A1:S103"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="19" customWidth="1"/>
@@ -1216,1327 +1175,1327 @@
     <col min="6" max="6" width="7.28515625" style="19" customWidth="1"/>
     <col min="7" max="7" width="9.140625" style="19"/>
     <col min="8" max="8" width="5" style="19" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5703125" style="19" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" style="19" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" style="19" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" style="19" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="9.140625" style="19"/>
     <col min="13" max="16" width="0" style="19" hidden="1" customWidth="1"/>
     <col min="17" max="16384" width="9.140625" style="19"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="66"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
     </row>
     <row r="2" spans="1:18" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="68" t="s">
+      <c r="A3" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="68" t="s">
+      <c r="A4" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="68"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="68"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="69" t="s">
+      <c r="A5" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="69"/>
-      <c r="C5" s="69"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="69"/>
-      <c r="I5" s="69"/>
-      <c r="J5" s="69"/>
-      <c r="K5" s="69"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="59"/>
     </row>
     <row r="6" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
+      <c r="A6" s="54" t="s">
+        <v>79</v>
+      </c>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="65" t="s">
-        <v>28</v>
-      </c>
-      <c r="I6" s="65"/>
-      <c r="J6" s="65"/>
-      <c r="K6" s="65"/>
+      <c r="H6" s="55" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="55"/>
+      <c r="J6" s="55"/>
+      <c r="K6" s="55"/>
     </row>
     <row r="7" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="59" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="59"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59"/>
-      <c r="F7" s="59"/>
+      <c r="A7" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
       <c r="G7" s="11"/>
-      <c r="H7" s="60" t="s">
-        <v>23</v>
-      </c>
-      <c r="I7" s="60"/>
-      <c r="J7" s="60"/>
-      <c r="K7" s="60"/>
+      <c r="H7" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="I7" s="50"/>
+      <c r="J7" s="50"/>
+      <c r="K7" s="50"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="C8" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="D8" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="E8" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="F8" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="G8" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="H8" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="I8" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="J8" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="14" t="s">
+      <c r="K8" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="K8" s="15" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" s="37" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="39">
+    </row>
+    <row r="9" spans="1:18" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
         <v>1</v>
       </c>
-      <c r="B9" s="40" t="s">
+      <c r="B9" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="41" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="43" t="s">
-        <v>41</v>
-      </c>
-      <c r="G9" s="43"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="45"/>
-      <c r="J9" s="46"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="42"/>
       <c r="K9" s="5"/>
     </row>
-    <row r="10" spans="1:18" s="37" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="47"/>
-      <c r="B10" s="48" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="49">
+    <row r="10" spans="1:18" s="36" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="16"/>
+      <c r="B10" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="44">
         <f>4</f>
         <v>4</v>
       </c>
-      <c r="D10" s="50">
+      <c r="D10" s="9">
         <f>(12+1+2)/3.281</f>
         <v>4.5717768972874122</v>
       </c>
-      <c r="E10" s="50">
+      <c r="E10" s="9">
         <v>6.5</v>
       </c>
-      <c r="F10" s="50">
+      <c r="F10" s="9">
         <f t="shared" ref="F10:F15" si="0">PRODUCT(C10:E10)</f>
         <v>118.86619932947272</v>
       </c>
-      <c r="G10" s="50">
+      <c r="G10" s="9">
         <f t="shared" ref="G10:G15" si="1">F10</f>
         <v>118.86619932947272</v>
       </c>
-      <c r="H10" s="46"/>
-      <c r="I10" s="46"/>
-      <c r="J10" s="46"/>
-      <c r="K10" s="38"/>
-    </row>
-    <row r="11" spans="1:18" s="37" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="47"/>
-      <c r="B11" s="48" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" s="49">
+      <c r="H10" s="42"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="27"/>
+    </row>
+    <row r="11" spans="1:18" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="16"/>
+      <c r="B11" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="44">
         <v>4</v>
       </c>
-      <c r="D11" s="50">
+      <c r="D11" s="9">
         <f>12/3.281</f>
         <v>3.6574215178299299</v>
       </c>
-      <c r="E11" s="50">
+      <c r="E11" s="9">
         <v>6.5</v>
       </c>
-      <c r="F11" s="50">
+      <c r="F11" s="9">
         <f t="shared" si="0"/>
         <v>95.092959463578183</v>
       </c>
-      <c r="G11" s="50">
+      <c r="G11" s="9">
         <f t="shared" si="1"/>
         <v>95.092959463578183</v>
       </c>
-      <c r="H11" s="46"/>
-      <c r="I11" s="46"/>
-      <c r="J11" s="46"/>
-      <c r="K11" s="38"/>
-      <c r="Q11" s="37">
+      <c r="H11" s="42"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="42"/>
+      <c r="K11" s="27"/>
+      <c r="Q11" s="36">
         <f>PRODUCT(C11:D11)</f>
         <v>14.629686071319719</v>
       </c>
-      <c r="R11" s="37">
+      <c r="R11" s="36">
         <f>CONVERT(Q11,"m","ft")</f>
         <v>47.997657714303543</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="37" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" s="47"/>
-      <c r="B12" s="48" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="49">
+    <row r="12" spans="1:18" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A12" s="16"/>
+      <c r="B12" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="44">
         <v>2</v>
       </c>
-      <c r="D12" s="50">
+      <c r="D12" s="9">
         <f>12/3.281</f>
         <v>3.6574215178299299</v>
       </c>
-      <c r="E12" s="50">
+      <c r="E12" s="9">
         <v>6.5</v>
       </c>
-      <c r="F12" s="50">
+      <c r="F12" s="9">
         <f t="shared" si="0"/>
         <v>47.546479731789091</v>
       </c>
-      <c r="G12" s="50">
+      <c r="G12" s="9">
         <f t="shared" si="1"/>
         <v>47.546479731789091</v>
       </c>
-      <c r="H12" s="46"/>
-      <c r="I12" s="46"/>
-      <c r="J12" s="46"/>
-      <c r="K12" s="38"/>
-    </row>
-    <row r="13" spans="1:18" s="37" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="47"/>
-      <c r="B13" s="48" t="s">
-        <v>49</v>
-      </c>
-      <c r="C13" s="49">
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="27"/>
+    </row>
+    <row r="13" spans="1:18" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="16"/>
+      <c r="B13" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="44">
         <v>4</v>
       </c>
-      <c r="D13" s="50">
+      <c r="D13" s="9">
         <f>5.33/3.281</f>
         <v>1.6245047241694606</v>
       </c>
-      <c r="E13" s="50">
+      <c r="E13" s="9">
         <v>6.5</v>
       </c>
-      <c r="F13" s="50">
+      <c r="F13" s="9">
         <f t="shared" si="0"/>
         <v>42.237122828405973</v>
       </c>
-      <c r="G13" s="50">
+      <c r="G13" s="9">
         <f t="shared" si="1"/>
         <v>42.237122828405973</v>
       </c>
-      <c r="H13" s="46"/>
-      <c r="I13" s="46"/>
-      <c r="J13" s="46"/>
-      <c r="K13" s="38"/>
-    </row>
-    <row r="14" spans="1:18" s="37" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" s="47"/>
-      <c r="B14" s="48" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" s="49">
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="27"/>
+    </row>
+    <row r="14" spans="1:18" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="16"/>
+      <c r="B14" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="44">
         <v>2</v>
       </c>
-      <c r="D14" s="50">
+      <c r="D14" s="9">
         <f>8.25/3.281</f>
         <v>2.5144772935080768</v>
       </c>
-      <c r="E14" s="50">
+      <c r="E14" s="9">
         <v>4.43</v>
       </c>
-      <c r="F14" s="50">
+      <c r="F14" s="9">
         <f t="shared" si="0"/>
         <v>22.278268820481561</v>
       </c>
-      <c r="G14" s="50">
+      <c r="G14" s="9">
         <f t="shared" si="1"/>
         <v>22.278268820481561</v>
       </c>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="38"/>
-    </row>
-    <row r="15" spans="1:18" s="37" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="47"/>
-      <c r="B15" s="48" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" s="49">
+      <c r="H14" s="42"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="27"/>
+    </row>
+    <row r="15" spans="1:18" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="16"/>
+      <c r="B15" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="44">
         <f>2*4</f>
         <v>8</v>
       </c>
-      <c r="D15" s="50">
+      <c r="D15" s="9">
         <f>6/3.281</f>
         <v>1.8287107589149649</v>
       </c>
-      <c r="E15" s="50">
+      <c r="E15" s="9">
         <v>4.43</v>
       </c>
-      <c r="F15" s="50">
+      <c r="F15" s="9">
         <f t="shared" si="0"/>
         <v>64.809509295946356</v>
       </c>
-      <c r="G15" s="50">
+      <c r="G15" s="9">
         <f t="shared" si="1"/>
         <v>64.809509295946356</v>
       </c>
-      <c r="H15" s="46"/>
-      <c r="I15" s="46"/>
-      <c r="J15" s="46"/>
-      <c r="K15" s="38"/>
-    </row>
-    <row r="16" spans="1:18" s="37" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="47"/>
-      <c r="B16" s="48" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" s="49">
+      <c r="H15" s="42"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="42"/>
+      <c r="K15" s="27"/>
+    </row>
+    <row r="16" spans="1:18" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A16" s="16"/>
+      <c r="B16" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="44">
         <f>4</f>
         <v>4</v>
       </c>
-      <c r="D16" s="50">
+      <c r="D16" s="9">
         <f>9.5/3.281</f>
         <v>2.895458701615361</v>
       </c>
-      <c r="E16" s="50">
+      <c r="E16" s="9">
         <v>4.43</v>
       </c>
-      <c r="F16" s="50">
+      <c r="F16" s="9">
         <f t="shared" ref="F16" si="2">PRODUCT(C16:E16)</f>
         <v>51.307528192624197</v>
       </c>
-      <c r="G16" s="50">
+      <c r="G16" s="9">
         <f t="shared" ref="G16" si="3">F16</f>
         <v>51.307528192624197</v>
       </c>
-      <c r="H16" s="46"/>
-      <c r="I16" s="46"/>
-      <c r="J16" s="46"/>
-      <c r="K16" s="38"/>
-    </row>
-    <row r="17" spans="1:11" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="47"/>
-      <c r="B17" s="48"/>
-      <c r="C17" s="49">
+      <c r="H16" s="42"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="42"/>
+      <c r="K16" s="27"/>
+    </row>
+    <row r="17" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="16"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="44">
         <f>4</f>
         <v>4</v>
       </c>
-      <c r="D17" s="50">
+      <c r="D17" s="9">
         <f>14.083/3.281</f>
         <v>4.2922889362999088</v>
       </c>
-      <c r="E17" s="50">
+      <c r="E17" s="9">
         <v>4.43</v>
       </c>
-      <c r="F17" s="50">
+      <c r="F17" s="9">
         <f t="shared" ref="F17:F18" si="4">PRODUCT(C17:E17)</f>
         <v>76.059359951234384</v>
       </c>
-      <c r="G17" s="50">
+      <c r="G17" s="9">
         <f t="shared" ref="G17:G18" si="5">F17</f>
         <v>76.059359951234384</v>
       </c>
-      <c r="H17" s="46"/>
-      <c r="I17" s="46"/>
-      <c r="J17" s="46"/>
-      <c r="K17" s="38"/>
-    </row>
-    <row r="18" spans="1:11" s="37" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="47"/>
-      <c r="B18" s="48" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18" s="49">
+      <c r="H17" s="42"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="42"/>
+      <c r="K17" s="27"/>
+    </row>
+    <row r="18" spans="1:11" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="16"/>
+      <c r="B18" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="44">
         <f>4*2</f>
         <v>8</v>
       </c>
-      <c r="D18" s="50">
+      <c r="D18" s="9">
         <f>6.42/3.281</f>
         <v>1.9567205120390123</v>
       </c>
-      <c r="E18" s="50">
+      <c r="E18" s="9">
         <v>4.43</v>
       </c>
-      <c r="F18" s="50">
+      <c r="F18" s="9">
         <f t="shared" si="4"/>
         <v>69.346174946662586</v>
       </c>
-      <c r="G18" s="50">
+      <c r="G18" s="9">
         <f t="shared" si="5"/>
         <v>69.346174946662586</v>
       </c>
-      <c r="H18" s="46"/>
-      <c r="I18" s="46"/>
-      <c r="J18" s="46"/>
-      <c r="K18" s="38"/>
-    </row>
-    <row r="19" spans="1:11" s="37" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A19" s="47"/>
-      <c r="B19" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="C19" s="49">
+      <c r="H18" s="42"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="42"/>
+      <c r="K18" s="27"/>
+    </row>
+    <row r="19" spans="1:11" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A19" s="16"/>
+      <c r="B19" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="44">
         <v>4</v>
       </c>
-      <c r="D19" s="50">
+      <c r="D19" s="9">
         <f>8/3.281</f>
         <v>2.4382810118866196</v>
       </c>
-      <c r="E19" s="50">
+      <c r="E19" s="9">
         <v>4.43</v>
       </c>
-      <c r="F19" s="50">
+      <c r="F19" s="9">
         <f t="shared" ref="F19" si="6">PRODUCT(C19:E19)</f>
         <v>43.206339530630899</v>
       </c>
-      <c r="G19" s="50">
+      <c r="G19" s="9">
         <f t="shared" ref="G19" si="7">F19</f>
         <v>43.206339530630899</v>
       </c>
-      <c r="H19" s="46"/>
-      <c r="I19" s="46"/>
-      <c r="J19" s="46"/>
-      <c r="K19" s="38"/>
-    </row>
-    <row r="20" spans="1:11" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="47"/>
-      <c r="B20" s="48"/>
-      <c r="C20" s="49">
+      <c r="H19" s="42"/>
+      <c r="I19" s="42"/>
+      <c r="J19" s="42"/>
+      <c r="K19" s="27"/>
+    </row>
+    <row r="20" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="16"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="44">
         <v>4</v>
       </c>
-      <c r="D20" s="50">
+      <c r="D20" s="9">
         <f>2.5/3.281</f>
         <v>0.76196281621456874</v>
       </c>
-      <c r="E20" s="50">
+      <c r="E20" s="9">
         <v>5.43</v>
       </c>
-      <c r="F20" s="50">
+      <c r="F20" s="9">
         <f t="shared" ref="F20:F21" si="8">PRODUCT(C20:E20)</f>
         <v>16.549832368180432</v>
       </c>
-      <c r="G20" s="50">
+      <c r="G20" s="9">
         <f t="shared" ref="G20:G21" si="9">F20</f>
         <v>16.549832368180432</v>
       </c>
-      <c r="H20" s="46"/>
-      <c r="I20" s="46"/>
-      <c r="J20" s="46"/>
-      <c r="K20" s="38"/>
-    </row>
-    <row r="21" spans="1:11" s="37" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A21" s="47"/>
-      <c r="B21" s="48" t="s">
-        <v>55</v>
-      </c>
-      <c r="C21" s="49">
+      <c r="H20" s="42"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="42"/>
+      <c r="K20" s="27"/>
+    </row>
+    <row r="21" spans="1:11" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A21" s="16"/>
+      <c r="B21" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="44">
         <f>4*2</f>
         <v>8</v>
       </c>
-      <c r="D21" s="50">
+      <c r="D21" s="9">
         <f>4.17/3.281</f>
         <v>1.2709539774459007</v>
       </c>
-      <c r="E21" s="50">
+      <c r="E21" s="9">
         <v>4.43</v>
       </c>
-      <c r="F21" s="50">
+      <c r="F21" s="9">
         <f t="shared" si="8"/>
         <v>45.042608960682713</v>
       </c>
-      <c r="G21" s="50">
+      <c r="G21" s="9">
         <f t="shared" si="9"/>
         <v>45.042608960682713</v>
       </c>
-      <c r="H21" s="46"/>
-      <c r="I21" s="46"/>
-      <c r="J21" s="46"/>
-      <c r="K21" s="38"/>
-    </row>
-    <row r="22" spans="1:11" s="37" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" s="47"/>
-      <c r="B22" s="48" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" s="49">
+      <c r="H21" s="42"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="42"/>
+      <c r="K21" s="27"/>
+    </row>
+    <row r="22" spans="1:11" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A22" s="16"/>
+      <c r="B22" s="43" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="44">
         <v>6</v>
       </c>
-      <c r="D22" s="50">
+      <c r="D22" s="9">
         <v>1.5</v>
       </c>
-      <c r="E22" s="50">
+      <c r="E22" s="9">
         <v>3.01</v>
       </c>
-      <c r="F22" s="50">
+      <c r="F22" s="9">
         <f t="shared" ref="F22" si="10">PRODUCT(C22:E22)</f>
         <v>27.089999999999996</v>
       </c>
-      <c r="G22" s="50">
+      <c r="G22" s="9">
         <f t="shared" ref="G22" si="11">F22</f>
         <v>27.089999999999996</v>
       </c>
-      <c r="H22" s="46"/>
-      <c r="I22" s="46"/>
-      <c r="J22" s="46"/>
-      <c r="K22" s="38"/>
-    </row>
-    <row r="23" spans="1:11" s="37" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A23" s="47"/>
-      <c r="B23" s="48" t="s">
-        <v>75</v>
-      </c>
-      <c r="C23" s="49">
+      <c r="H22" s="42"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="42"/>
+      <c r="K22" s="27"/>
+    </row>
+    <row r="23" spans="1:11" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A23" s="16"/>
+      <c r="B23" s="43" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" s="44">
         <v>1</v>
       </c>
-      <c r="D23" s="50">
+      <c r="D23" s="9">
         <f>36/3.281</f>
         <v>10.97226455348979</v>
       </c>
-      <c r="E23" s="50">
+      <c r="E23" s="9">
         <v>3.01</v>
       </c>
-      <c r="F23" s="50">
+      <c r="F23" s="9">
         <f t="shared" ref="F23" si="12">PRODUCT(C23:E23)</f>
         <v>33.026516306004268</v>
       </c>
-      <c r="G23" s="50">
+      <c r="G23" s="9">
         <f t="shared" ref="G23" si="13">F23</f>
         <v>33.026516306004268</v>
       </c>
-      <c r="H23" s="46"/>
-      <c r="I23" s="46"/>
-      <c r="J23" s="46"/>
-      <c r="K23" s="38"/>
-    </row>
-    <row r="24" spans="1:11" s="37" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A24" s="47"/>
-      <c r="B24" s="48" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" s="49">
+      <c r="H23" s="42"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="42"/>
+      <c r="K23" s="27"/>
+    </row>
+    <row r="24" spans="1:11" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A24" s="16"/>
+      <c r="B24" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" s="44">
         <v>2</v>
       </c>
-      <c r="D24" s="50">
+      <c r="D24" s="9">
         <f>(36-0.17*7)/3.281</f>
         <v>10.609570252971656</v>
       </c>
-      <c r="E24" s="50">
+      <c r="E24" s="9">
         <v>2.2599999999999998</v>
       </c>
-      <c r="F24" s="50">
+      <c r="F24" s="9">
         <f t="shared" ref="F24" si="14">PRODUCT(C24:E24)</f>
         <v>47.955257543431877</v>
       </c>
-      <c r="G24" s="50">
+      <c r="G24" s="9">
         <f t="shared" ref="G24" si="15">F24</f>
         <v>47.955257543431877</v>
       </c>
-      <c r="H24" s="46"/>
-      <c r="I24" s="46"/>
-      <c r="J24" s="46"/>
-      <c r="K24" s="38"/>
-    </row>
-    <row r="25" spans="1:11" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="39"/>
-      <c r="B25" s="48" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" s="41"/>
-      <c r="D25" s="51"/>
-      <c r="E25" s="52"/>
-      <c r="F25" s="52"/>
-      <c r="G25" s="46">
+      <c r="H24" s="42"/>
+      <c r="I24" s="42"/>
+      <c r="J24" s="42"/>
+      <c r="K24" s="27"/>
+    </row>
+    <row r="25" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="B25" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="3"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="42">
         <f>SUM(G10:G24)</f>
         <v>800.41415726912533</v>
       </c>
-      <c r="H25" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="I25" s="45">
+      <c r="H25" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="I25" s="6">
         <v>182.51</v>
       </c>
-      <c r="J25" s="46">
+      <c r="J25" s="42">
         <f>G25*I25</f>
         <v>146083.58784318806</v>
       </c>
       <c r="K25" s="5"/>
     </row>
-    <row r="26" spans="1:11" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="39"/>
-      <c r="B26" s="48" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" s="41"/>
-      <c r="D26" s="51"/>
-      <c r="E26" s="52"/>
-      <c r="F26" s="52"/>
-      <c r="G26" s="46"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="45"/>
-      <c r="J26" s="46">
+    <row r="26" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="B26" s="43" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" s="3"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="42"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="42">
         <f>0.13*G25*(1871.42/18.94)</f>
         <v>10281.332528276465</v>
       </c>
       <c r="K26" s="5"/>
     </row>
-    <row r="27" spans="1:11" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="39"/>
-      <c r="B27" s="48"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="51"/>
-      <c r="E27" s="52"/>
-      <c r="F27" s="52"/>
-      <c r="G27" s="46"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="45"/>
-      <c r="J27" s="46"/>
+    <row r="27" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="42"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="42"/>
       <c r="K27" s="5"/>
     </row>
-    <row r="28" spans="1:11" s="37" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="39">
+    <row r="28" spans="1:11" s="36" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
         <v>2</v>
       </c>
-      <c r="B28" s="40" t="s">
-        <v>63</v>
-      </c>
-      <c r="C28" s="41"/>
-      <c r="D28" s="51"/>
-      <c r="E28" s="52"/>
-      <c r="F28" s="52"/>
-      <c r="G28" s="46"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="45"/>
-      <c r="J28" s="46"/>
+      <c r="B28" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28" s="3"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="42"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="42"/>
       <c r="K28" s="5"/>
     </row>
-    <row r="29" spans="1:11" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="39"/>
-      <c r="B29" s="48" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29" s="41">
+    <row r="29" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="B29" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" s="3">
         <v>4</v>
       </c>
-      <c r="D29" s="51">
+      <c r="D29" s="4">
         <f>((15.833+6.5)/2)/3.281</f>
         <v>3.4033831149039924</v>
       </c>
-      <c r="E29" s="52">
+      <c r="E29" s="5">
         <f>5.33/3.281</f>
         <v>1.6245047241694606</v>
       </c>
-      <c r="F29" s="52"/>
-      <c r="G29" s="53">
+      <c r="F29" s="5"/>
+      <c r="G29" s="33">
         <f t="shared" ref="G29:G30" si="16">PRODUCT(C29:F29)</f>
         <v>22.115247793280439</v>
       </c>
-      <c r="H29" s="44"/>
-      <c r="I29" s="45"/>
-      <c r="J29" s="46"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="42"/>
       <c r="K29" s="5"/>
     </row>
-    <row r="30" spans="1:11" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="39"/>
-      <c r="B30" s="48" t="s">
-        <v>57</v>
-      </c>
-      <c r="C30" s="41">
+    <row r="30" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
+      <c r="B30" s="43" t="s">
+        <v>53</v>
+      </c>
+      <c r="C30" s="3">
         <v>4</v>
       </c>
-      <c r="D30" s="51">
+      <c r="D30" s="4">
         <f>((0+9.583)/2)/3.281</f>
         <v>1.4603779335568423</v>
       </c>
-      <c r="E30" s="52">
+      <c r="E30" s="5">
         <f>5.5/3.281</f>
         <v>1.6763181956720512</v>
       </c>
-      <c r="F30" s="52"/>
-      <c r="G30" s="53">
+      <c r="F30" s="5"/>
+      <c r="G30" s="33">
         <f t="shared" si="16"/>
         <v>9.7922324103171388</v>
       </c>
-      <c r="H30" s="44"/>
-      <c r="I30" s="45"/>
-      <c r="J30" s="46"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="42"/>
       <c r="K30" s="5"/>
     </row>
-    <row r="31" spans="1:11" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="39"/>
-      <c r="B31" s="48" t="s">
-        <v>42</v>
-      </c>
-      <c r="C31" s="41"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="52"/>
-      <c r="F31" s="52"/>
-      <c r="G31" s="46">
+    <row r="31" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2"/>
+      <c r="B31" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="3"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="42">
         <f>SUM(G29:G30)</f>
         <v>31.907480203597579</v>
       </c>
-      <c r="H31" s="44" t="s">
-        <v>58</v>
-      </c>
-      <c r="I31" s="45">
+      <c r="H31" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="I31" s="6">
         <v>1112.58</v>
       </c>
-      <c r="J31" s="46">
+      <c r="J31" s="42">
         <f>G31*I31</f>
         <v>35499.624324918594</v>
       </c>
       <c r="K31" s="5"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="47"/>
-      <c r="B32" s="54" t="s">
-        <v>59</v>
-      </c>
-      <c r="C32" s="55"/>
-      <c r="D32" s="55"/>
-      <c r="E32" s="55"/>
-      <c r="F32" s="55"/>
-      <c r="G32" s="55"/>
-      <c r="H32" s="55"/>
-      <c r="I32" s="55"/>
-      <c r="J32" s="56">
+      <c r="A32" s="16"/>
+      <c r="B32" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
+      <c r="J32" s="18">
         <f>0.13*G31*7050.67/10</f>
         <v>2924.5984748122914</v>
       </c>
       <c r="K32" s="17"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="47"/>
-      <c r="B33" s="54" t="s">
-        <v>60</v>
-      </c>
-      <c r="C33" s="55"/>
-      <c r="D33" s="55"/>
-      <c r="E33" s="55"/>
-      <c r="F33" s="55"/>
-      <c r="G33" s="55"/>
-      <c r="H33" s="55"/>
-      <c r="I33" s="55"/>
-      <c r="J33" s="56">
+      <c r="A33" s="16"/>
+      <c r="B33" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17"/>
+      <c r="J33" s="18">
         <f>0.13*G31*1023.75/10</f>
         <v>424.6486771596293</v>
       </c>
       <c r="K33" s="17"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="47"/>
-      <c r="B34" s="54" t="s">
-        <v>61</v>
-      </c>
-      <c r="C34" s="55"/>
-      <c r="D34" s="55"/>
-      <c r="E34" s="55"/>
-      <c r="F34" s="55"/>
-      <c r="G34" s="55"/>
-      <c r="H34" s="55"/>
-      <c r="I34" s="55"/>
-      <c r="J34" s="56">
+      <c r="A34" s="16"/>
+      <c r="B34" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="17"/>
+      <c r="J34" s="18">
         <f>0.13*G31*348.21/10</f>
         <v>144.43654786203126</v>
       </c>
       <c r="K34" s="17"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="47"/>
-      <c r="B35" s="54" t="s">
-        <v>62</v>
-      </c>
-      <c r="C35" s="55"/>
-      <c r="D35" s="55"/>
-      <c r="E35" s="55"/>
-      <c r="F35" s="55"/>
-      <c r="G35" s="55"/>
-      <c r="H35" s="55"/>
-      <c r="I35" s="55"/>
-      <c r="J35" s="56">
+      <c r="A35" s="16"/>
+      <c r="B35" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="17"/>
+      <c r="I35" s="17"/>
+      <c r="J35" s="18">
         <f>0.13*G31*165/10</f>
         <v>68.441545036716803</v>
       </c>
       <c r="K35" s="17"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="47"/>
-      <c r="B36" s="54"/>
-      <c r="C36" s="55"/>
-      <c r="D36" s="55"/>
-      <c r="E36" s="55"/>
-      <c r="F36" s="55"/>
-      <c r="G36" s="55"/>
-      <c r="H36" s="55"/>
-      <c r="I36" s="55"/>
-      <c r="J36" s="56"/>
+      <c r="A36" s="16"/>
+      <c r="B36" s="32"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="17"/>
+      <c r="J36" s="18"/>
       <c r="K36" s="17"/>
     </row>
     <row r="37" spans="1:11" ht="150" x14ac:dyDescent="0.25">
-      <c r="A37" s="47">
+      <c r="A37" s="16">
         <v>3</v>
       </c>
-      <c r="B37" s="70" t="s">
-        <v>64</v>
-      </c>
-      <c r="C37" s="55"/>
-      <c r="D37" s="55"/>
-      <c r="E37" s="55"/>
-      <c r="F37" s="55"/>
-      <c r="G37" s="55"/>
-      <c r="H37" s="55"/>
-      <c r="I37" s="55"/>
-      <c r="J37" s="56"/>
+      <c r="B37" s="45" t="s">
+        <v>60</v>
+      </c>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="17"/>
+      <c r="J37" s="18"/>
       <c r="K37" s="17"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="47"/>
-      <c r="B38" s="54" t="s">
-        <v>65</v>
-      </c>
-      <c r="C38" s="55">
+      <c r="A38" s="16"/>
+      <c r="B38" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="C38" s="17">
         <v>1</v>
       </c>
-      <c r="D38" s="53">
+      <c r="D38" s="33">
         <f>D47</f>
         <v>8.5</v>
       </c>
-      <c r="E38" s="55">
+      <c r="E38" s="17">
         <f>E47</f>
         <v>2</v>
       </c>
-      <c r="F38" s="55">
+      <c r="F38" s="17">
         <v>0.9</v>
       </c>
-      <c r="G38" s="53">
+      <c r="G38" s="33">
         <f t="shared" ref="G38:G42" si="17">PRODUCT(C38:F38)</f>
         <v>15.3</v>
       </c>
-      <c r="H38" s="55"/>
-      <c r="I38" s="55"/>
-      <c r="J38" s="56"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="18"/>
       <c r="K38" s="17"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="47"/>
-      <c r="B39" s="54"/>
-      <c r="C39" s="55">
+      <c r="A39" s="16"/>
+      <c r="B39" s="32"/>
+      <c r="C39" s="17">
         <v>1</v>
       </c>
-      <c r="D39" s="53">
+      <c r="D39" s="33">
         <f>D48</f>
         <v>5</v>
       </c>
-      <c r="E39" s="55">
+      <c r="E39" s="17">
         <f>E48</f>
         <v>1</v>
       </c>
-      <c r="F39" s="55">
+      <c r="F39" s="17">
         <v>0.75</v>
       </c>
-      <c r="G39" s="53">
+      <c r="G39" s="33">
         <f t="shared" si="17"/>
         <v>3.75</v>
       </c>
-      <c r="H39" s="55"/>
-      <c r="I39" s="55"/>
-      <c r="J39" s="56"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="17"/>
+      <c r="J39" s="18"/>
       <c r="K39" s="17"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="47"/>
-      <c r="B40" s="54" t="s">
-        <v>69</v>
-      </c>
-      <c r="C40" s="55">
+      <c r="A40" s="16"/>
+      <c r="B40" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="C40" s="17">
         <v>4</v>
       </c>
-      <c r="D40" s="53">
+      <c r="D40" s="33">
         <v>0.6</v>
       </c>
-      <c r="E40" s="55">
+      <c r="E40" s="17">
         <v>0.6</v>
       </c>
-      <c r="F40" s="55">
+      <c r="F40" s="17">
         <v>0.6</v>
       </c>
-      <c r="G40" s="53">
+      <c r="G40" s="33">
         <f t="shared" si="17"/>
         <v>0.86399999999999999</v>
       </c>
-      <c r="H40" s="55"/>
-      <c r="I40" s="55"/>
-      <c r="J40" s="56"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="18"/>
       <c r="K40" s="17"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="47"/>
-      <c r="B41" s="54" t="s">
-        <v>70</v>
-      </c>
-      <c r="C41" s="55">
+      <c r="A41" s="16"/>
+      <c r="B41" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="C41" s="17">
         <v>4</v>
       </c>
-      <c r="D41" s="53">
+      <c r="D41" s="33">
         <f>10.25/3.281</f>
         <v>3.1240475464797317</v>
       </c>
-      <c r="E41" s="55">
+      <c r="E41" s="17">
         <v>0.45</v>
       </c>
-      <c r="F41" s="53">
+      <c r="F41" s="33">
         <f>0.45+0.075</f>
         <v>0.52500000000000002</v>
       </c>
-      <c r="G41" s="53">
+      <c r="G41" s="33">
         <f t="shared" si="17"/>
         <v>2.9522249314233471</v>
       </c>
-      <c r="H41" s="55"/>
-      <c r="I41" s="55"/>
-      <c r="J41" s="56"/>
+      <c r="H41" s="17"/>
+      <c r="I41" s="17"/>
+      <c r="J41" s="18"/>
       <c r="K41" s="17"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="47"/>
-      <c r="B42" s="54" t="s">
-        <v>77</v>
-      </c>
-      <c r="C42" s="55">
+      <c r="A42" s="16"/>
+      <c r="B42" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="C42" s="17">
         <v>6</v>
       </c>
-      <c r="D42" s="53">
+      <c r="D42" s="33">
         <v>0.3</v>
       </c>
-      <c r="E42" s="55">
+      <c r="E42" s="17">
         <v>0.3</v>
       </c>
-      <c r="F42" s="53">
+      <c r="F42" s="33">
         <v>0.6</v>
       </c>
-      <c r="G42" s="53">
+      <c r="G42" s="33">
         <f t="shared" si="17"/>
         <v>0.32399999999999995</v>
       </c>
-      <c r="H42" s="55"/>
-      <c r="I42" s="55"/>
-      <c r="J42" s="56"/>
+      <c r="H42" s="17"/>
+      <c r="I42" s="17"/>
+      <c r="J42" s="18"/>
       <c r="K42" s="17"/>
     </row>
-    <row r="43" spans="1:11" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="39"/>
-      <c r="B43" s="48" t="s">
-        <v>42</v>
-      </c>
-      <c r="C43" s="41"/>
-      <c r="D43" s="51"/>
-      <c r="E43" s="52"/>
-      <c r="F43" s="52"/>
-      <c r="G43" s="46">
+    <row r="43" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2"/>
+      <c r="B43" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="C43" s="3"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="42">
         <f>SUM(G38:G42)</f>
         <v>23.190224931423352</v>
       </c>
-      <c r="H43" s="44" t="s">
-        <v>67</v>
-      </c>
-      <c r="I43" s="45">
+      <c r="H43" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I43" s="6">
         <v>62.95</v>
       </c>
-      <c r="J43" s="46">
+      <c r="J43" s="42">
         <f>G43*I43</f>
         <v>1459.8246594331001</v>
       </c>
       <c r="K43" s="5"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" s="47"/>
-      <c r="B44" s="54" t="s">
-        <v>66</v>
-      </c>
-      <c r="C44" s="55"/>
-      <c r="D44" s="55"/>
-      <c r="E44" s="55"/>
-      <c r="F44" s="55"/>
-      <c r="G44" s="55"/>
-      <c r="H44" s="55"/>
-      <c r="I44" s="55"/>
-      <c r="J44" s="56">
+      <c r="A44" s="16"/>
+      <c r="B44" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="17"/>
+      <c r="F44" s="17"/>
+      <c r="G44" s="17"/>
+      <c r="H44" s="17"/>
+      <c r="I44" s="17"/>
+      <c r="J44" s="18">
         <f>0.13*G43*18612/360</f>
         <v>155.86150176409637</v>
       </c>
       <c r="K44" s="17"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="47"/>
-      <c r="B45" s="54"/>
-      <c r="C45" s="55"/>
-      <c r="D45" s="55"/>
-      <c r="E45" s="55"/>
-      <c r="F45" s="55"/>
-      <c r="G45" s="55"/>
-      <c r="H45" s="55"/>
-      <c r="I45" s="55"/>
-      <c r="J45" s="56"/>
+      <c r="A45" s="16"/>
+      <c r="B45" s="32"/>
+      <c r="C45" s="17"/>
+      <c r="D45" s="17"/>
+      <c r="E45" s="17"/>
+      <c r="F45" s="17"/>
+      <c r="G45" s="17"/>
+      <c r="H45" s="17"/>
+      <c r="I45" s="17"/>
+      <c r="J45" s="18"/>
       <c r="K45" s="17"/>
     </row>
     <row r="46" spans="1:11" ht="105" x14ac:dyDescent="0.25">
-      <c r="A46" s="47">
+      <c r="A46" s="16">
         <v>4</v>
       </c>
-      <c r="B46" s="70" t="s">
-        <v>29</v>
-      </c>
-      <c r="C46" s="55"/>
-      <c r="D46" s="55"/>
-      <c r="E46" s="55"/>
-      <c r="F46" s="55"/>
-      <c r="G46" s="55"/>
-      <c r="H46" s="55"/>
-      <c r="I46" s="55"/>
-      <c r="J46" s="56"/>
+      <c r="B46" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="C46" s="17"/>
+      <c r="D46" s="17"/>
+      <c r="E46" s="17"/>
+      <c r="F46" s="17"/>
+      <c r="G46" s="17"/>
+      <c r="H46" s="17"/>
+      <c r="I46" s="17"/>
+      <c r="J46" s="18"/>
       <c r="K46" s="17"/>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" s="47"/>
-      <c r="B47" s="54" t="s">
-        <v>65</v>
-      </c>
-      <c r="C47" s="55">
+      <c r="A47" s="16"/>
+      <c r="B47" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="C47" s="17">
         <v>1</v>
       </c>
-      <c r="D47" s="53">
+      <c r="D47" s="33">
         <f>D58</f>
         <v>8.5</v>
       </c>
-      <c r="E47" s="55">
+      <c r="E47" s="17">
         <f>E58</f>
         <v>2</v>
       </c>
-      <c r="F47" s="55">
+      <c r="F47" s="17">
         <v>0.15</v>
       </c>
-      <c r="G47" s="53">
+      <c r="G47" s="33">
         <f t="shared" ref="G47:G53" si="18">PRODUCT(C47:F47)</f>
         <v>2.5499999999999998</v>
       </c>
-      <c r="H47" s="55"/>
-      <c r="I47" s="55"/>
-      <c r="J47" s="56"/>
+      <c r="H47" s="17"/>
+      <c r="I47" s="17"/>
+      <c r="J47" s="18"/>
       <c r="K47" s="17"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A48" s="47"/>
-      <c r="B48" s="54"/>
-      <c r="C48" s="55">
+      <c r="A48" s="16"/>
+      <c r="B48" s="32"/>
+      <c r="C48" s="17">
         <v>1</v>
       </c>
-      <c r="D48" s="53">
+      <c r="D48" s="33">
         <f>D60</f>
         <v>5</v>
       </c>
-      <c r="E48" s="55">
+      <c r="E48" s="17">
         <f>E60</f>
         <v>1</v>
       </c>
-      <c r="F48" s="55">
+      <c r="F48" s="17">
         <v>0.15</v>
       </c>
-      <c r="G48" s="53">
+      <c r="G48" s="33">
         <f t="shared" si="18"/>
         <v>0.75</v>
       </c>
-      <c r="H48" s="55"/>
-      <c r="I48" s="55"/>
-      <c r="J48" s="56"/>
+      <c r="H48" s="17"/>
+      <c r="I48" s="17"/>
+      <c r="J48" s="18"/>
       <c r="K48" s="17"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A49" s="47"/>
-      <c r="B49" s="54" t="str">
+      <c r="A49" s="16"/>
+      <c r="B49" s="32" t="str">
         <f>B40</f>
         <v>-for footing of vertical post</v>
       </c>
-      <c r="C49" s="55">
+      <c r="C49" s="17">
         <f>C40</f>
         <v>4</v>
       </c>
-      <c r="D49" s="53">
+      <c r="D49" s="33">
         <f>D40</f>
         <v>0.6</v>
       </c>
-      <c r="E49" s="55">
+      <c r="E49" s="17">
         <f>E40</f>
         <v>0.6</v>
       </c>
-      <c r="F49" s="55">
+      <c r="F49" s="17">
         <v>0.15</v>
       </c>
-      <c r="G49" s="53">
+      <c r="G49" s="33">
         <f t="shared" si="18"/>
         <v>0.216</v>
       </c>
-      <c r="H49" s="55"/>
-      <c r="I49" s="55"/>
-      <c r="J49" s="56"/>
+      <c r="H49" s="17"/>
+      <c r="I49" s="17"/>
+      <c r="J49" s="18"/>
       <c r="K49" s="17"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A50" s="47"/>
-      <c r="B50" s="54" t="str">
+      <c r="A50" s="16"/>
+      <c r="B50" s="32" t="str">
         <f>B41</f>
         <v>-for plinth level</v>
       </c>
-      <c r="C50" s="55">
+      <c r="C50" s="17">
         <f>C41</f>
         <v>4</v>
       </c>
-      <c r="D50" s="53">
+      <c r="D50" s="33">
         <f>10.75/3.281</f>
         <v>3.2764401097226452</v>
       </c>
-      <c r="E50" s="55">
+      <c r="E50" s="17">
         <v>0.45</v>
       </c>
-      <c r="F50" s="55">
+      <c r="F50" s="17">
         <v>0.15</v>
       </c>
-      <c r="G50" s="53">
+      <c r="G50" s="33">
         <f t="shared" si="18"/>
         <v>0.88463882962511431</v>
       </c>
-      <c r="H50" s="55"/>
-      <c r="I50" s="55"/>
-      <c r="J50" s="56"/>
+      <c r="H50" s="17"/>
+      <c r="I50" s="17"/>
+      <c r="J50" s="18"/>
       <c r="K50" s="17"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A51" s="47"/>
-      <c r="B51" s="54"/>
-      <c r="C51" s="55">
+      <c r="A51" s="16"/>
+      <c r="B51" s="32"/>
+      <c r="C51" s="17">
         <v>1</v>
       </c>
-      <c r="D51" s="53">
+      <c r="D51" s="33">
         <f>10.75/3.281</f>
         <v>3.2764401097226452</v>
       </c>
-      <c r="E51" s="53">
+      <c r="E51" s="33">
         <f>10.75/3.281</f>
         <v>3.2764401097226452</v>
       </c>
-      <c r="F51" s="55">
+      <c r="F51" s="17">
         <v>0.15</v>
       </c>
-      <c r="G51" s="53">
+      <c r="G51" s="33">
         <f t="shared" si="18"/>
         <v>1.6102589688899007</v>
       </c>
-      <c r="H51" s="55"/>
-      <c r="I51" s="55"/>
-      <c r="J51" s="56"/>
+      <c r="H51" s="17"/>
+      <c r="I51" s="17"/>
+      <c r="J51" s="18"/>
       <c r="K51" s="17"/>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A52" s="47"/>
-      <c r="B52" s="54" t="s">
-        <v>71</v>
-      </c>
-      <c r="C52" s="55">
+      <c r="A52" s="16"/>
+      <c r="B52" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="C52" s="17">
         <v>-1</v>
       </c>
-      <c r="D52" s="53">
+      <c r="D52" s="33">
         <v>1.5</v>
       </c>
-      <c r="E52" s="53">
+      <c r="E52" s="33">
         <v>1.8</v>
       </c>
-      <c r="F52" s="55">
+      <c r="F52" s="17">
         <v>0.15</v>
       </c>
-      <c r="G52" s="53">
+      <c r="G52" s="33">
         <f t="shared" si="18"/>
         <v>-0.40500000000000003</v>
       </c>
-      <c r="H52" s="55"/>
-      <c r="I52" s="55"/>
-      <c r="J52" s="56"/>
+      <c r="H52" s="17"/>
+      <c r="I52" s="17"/>
+      <c r="J52" s="18"/>
       <c r="K52" s="17"/>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A53" s="47"/>
-      <c r="B53" s="54" t="str">
+      <c r="A53" s="16"/>
+      <c r="B53" s="32" t="str">
         <f>B42</f>
         <v>-for railing</v>
       </c>
-      <c r="C53" s="55">
+      <c r="C53" s="17">
         <f>C42</f>
         <v>6</v>
       </c>
-      <c r="D53" s="53">
+      <c r="D53" s="33">
         <f>D42</f>
         <v>0.3</v>
       </c>
-      <c r="E53" s="53">
+      <c r="E53" s="33">
         <f>E42</f>
         <v>0.3</v>
       </c>
-      <c r="F53" s="55">
+      <c r="F53" s="17">
         <v>0.15</v>
       </c>
-      <c r="G53" s="53">
+      <c r="G53" s="33">
         <f t="shared" si="18"/>
         <v>8.0999999999999989E-2</v>
       </c>
-      <c r="H53" s="55"/>
-      <c r="I53" s="55"/>
-      <c r="J53" s="56"/>
+      <c r="H53" s="17"/>
+      <c r="I53" s="17"/>
+      <c r="J53" s="18"/>
       <c r="K53" s="17"/>
     </row>
-    <row r="54" spans="1:11" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="39"/>
-      <c r="B54" s="48" t="s">
-        <v>42</v>
-      </c>
-      <c r="C54" s="41"/>
-      <c r="D54" s="51"/>
-      <c r="E54" s="52"/>
-      <c r="F54" s="52"/>
-      <c r="G54" s="46">
+    <row r="54" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="2"/>
+      <c r="B54" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="C54" s="3"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="5"/>
+      <c r="G54" s="42">
         <f>SUM(G47:G53)</f>
         <v>5.6868977985150151</v>
       </c>
-      <c r="H54" s="44" t="s">
-        <v>67</v>
-      </c>
-      <c r="I54" s="45">
+      <c r="H54" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I54" s="6">
         <v>4458.5200000000004</v>
       </c>
-      <c r="J54" s="46">
+      <c r="J54" s="42">
         <f>G54*I54</f>
         <v>25355.147572635167</v>
       </c>
       <c r="K54" s="5"/>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A55" s="47"/>
-      <c r="B55" s="54" t="s">
-        <v>35</v>
-      </c>
-      <c r="C55" s="55"/>
-      <c r="D55" s="55"/>
-      <c r="E55" s="55"/>
-      <c r="F55" s="55"/>
-      <c r="G55" s="55"/>
-      <c r="H55" s="55"/>
-      <c r="I55" s="55"/>
-      <c r="J55" s="56">
+      <c r="A55" s="16"/>
+      <c r="B55" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="C55" s="17"/>
+      <c r="D55" s="17"/>
+      <c r="E55" s="17"/>
+      <c r="F55" s="17"/>
+      <c r="G55" s="17"/>
+      <c r="H55" s="17"/>
+      <c r="I55" s="17"/>
+      <c r="J55" s="18">
         <f>0.13*G54*15452.64/5</f>
         <v>2284.8171943283714</v>
       </c>
       <c r="K55" s="17"/>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" s="47"/>
-      <c r="B56" s="70"/>
-      <c r="C56" s="55"/>
-      <c r="D56" s="55"/>
-      <c r="E56" s="55"/>
-      <c r="F56" s="55"/>
-      <c r="G56" s="55"/>
-      <c r="H56" s="55"/>
-      <c r="I56" s="55"/>
-      <c r="J56" s="56"/>
+      <c r="A56" s="16"/>
+      <c r="B56" s="45"/>
+      <c r="C56" s="17"/>
+      <c r="D56" s="17"/>
+      <c r="E56" s="17"/>
+      <c r="F56" s="17"/>
+      <c r="G56" s="17"/>
+      <c r="H56" s="17"/>
+      <c r="I56" s="17"/>
+      <c r="J56" s="18"/>
       <c r="K56" s="17"/>
     </row>
-    <row r="57" spans="1:11" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A57" s="16">
         <v>5</v>
       </c>
-      <c r="B57" s="35" t="s">
-        <v>30</v>
+      <c r="B57" s="46" t="s">
+        <v>27</v>
       </c>
       <c r="C57" s="17"/>
       <c r="D57" s="17"/>
@@ -2549,340 +2508,340 @@
       <c r="K57" s="17"/>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A58" s="47"/>
-      <c r="B58" s="54" t="s">
-        <v>65</v>
-      </c>
-      <c r="C58" s="55">
+      <c r="A58" s="16"/>
+      <c r="B58" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="C58" s="17">
         <v>1</v>
       </c>
-      <c r="D58" s="53">
+      <c r="D58" s="33">
         <f>D75</f>
         <v>8.5</v>
       </c>
-      <c r="E58" s="53">
+      <c r="E58" s="33">
         <f>F75/2</f>
         <v>2</v>
       </c>
-      <c r="F58" s="55">
+      <c r="F58" s="17">
         <v>0.05</v>
       </c>
-      <c r="G58" s="53">
+      <c r="G58" s="33">
         <f t="shared" ref="G58:G66" si="19">PRODUCT(C58:F58)</f>
         <v>0.85000000000000009</v>
       </c>
-      <c r="H58" s="55"/>
-      <c r="I58" s="55"/>
-      <c r="J58" s="56"/>
+      <c r="H58" s="17"/>
+      <c r="I58" s="17"/>
+      <c r="J58" s="18"/>
       <c r="K58" s="17"/>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A59" s="47"/>
-      <c r="B59" s="54"/>
-      <c r="C59" s="55">
+      <c r="A59" s="16"/>
+      <c r="B59" s="32"/>
+      <c r="C59" s="17">
         <v>1</v>
       </c>
-      <c r="D59" s="53">
+      <c r="D59" s="33">
         <f>D58</f>
         <v>8.5</v>
       </c>
-      <c r="E59" s="55">
+      <c r="E59" s="17">
         <v>0.45</v>
       </c>
-      <c r="F59" s="55">
+      <c r="F59" s="17">
         <v>0.05</v>
       </c>
-      <c r="G59" s="53">
+      <c r="G59" s="33">
         <f t="shared" si="19"/>
         <v>0.19125000000000003</v>
       </c>
-      <c r="H59" s="55"/>
-      <c r="I59" s="55"/>
-      <c r="J59" s="56"/>
+      <c r="H59" s="17"/>
+      <c r="I59" s="17"/>
+      <c r="J59" s="18"/>
       <c r="K59" s="17"/>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A60" s="47"/>
-      <c r="B60" s="54"/>
-      <c r="C60" s="55">
+      <c r="A60" s="16"/>
+      <c r="B60" s="32"/>
+      <c r="C60" s="17">
         <v>1</v>
       </c>
-      <c r="D60" s="53">
+      <c r="D60" s="33">
         <f>D76</f>
         <v>5</v>
       </c>
-      <c r="E60" s="55">
+      <c r="E60" s="17">
         <f>F76/2</f>
         <v>1</v>
       </c>
-      <c r="F60" s="55">
+      <c r="F60" s="17">
         <v>0.05</v>
       </c>
-      <c r="G60" s="53">
+      <c r="G60" s="33">
         <f t="shared" si="19"/>
         <v>0.25</v>
       </c>
-      <c r="H60" s="55"/>
-      <c r="I60" s="55"/>
-      <c r="J60" s="56"/>
+      <c r="H60" s="17"/>
+      <c r="I60" s="17"/>
+      <c r="J60" s="18"/>
       <c r="K60" s="17"/>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A61" s="47"/>
-      <c r="B61" s="54"/>
-      <c r="C61" s="55">
+      <c r="A61" s="16"/>
+      <c r="B61" s="32"/>
+      <c r="C61" s="17">
         <v>1</v>
       </c>
-      <c r="D61" s="53">
+      <c r="D61" s="33">
         <f>D76</f>
         <v>5</v>
       </c>
-      <c r="E61" s="55">
+      <c r="E61" s="17">
         <v>0.45</v>
       </c>
-      <c r="F61" s="55">
+      <c r="F61" s="17">
         <v>0.05</v>
       </c>
-      <c r="G61" s="53">
+      <c r="G61" s="33">
         <f t="shared" si="19"/>
         <v>0.1125</v>
       </c>
-      <c r="H61" s="55"/>
-      <c r="I61" s="55"/>
-      <c r="J61" s="56"/>
+      <c r="H61" s="17"/>
+      <c r="I61" s="17"/>
+      <c r="J61" s="18"/>
       <c r="K61" s="17"/>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A62" s="47"/>
-      <c r="B62" s="54" t="str">
+      <c r="A62" s="16"/>
+      <c r="B62" s="32" t="str">
         <f>B49</f>
         <v>-for footing of vertical post</v>
       </c>
-      <c r="C62" s="55">
+      <c r="C62" s="17">
         <v>4</v>
       </c>
-      <c r="D62" s="53">
+      <c r="D62" s="33">
         <v>0.6</v>
       </c>
-      <c r="E62" s="55">
+      <c r="E62" s="17">
         <v>0.6</v>
       </c>
-      <c r="F62" s="55">
+      <c r="F62" s="17">
         <v>0.3</v>
       </c>
-      <c r="G62" s="53">
+      <c r="G62" s="33">
         <f t="shared" si="19"/>
         <v>0.432</v>
       </c>
-      <c r="H62" s="55"/>
-      <c r="I62" s="55"/>
-      <c r="J62" s="56"/>
+      <c r="H62" s="17"/>
+      <c r="I62" s="17"/>
+      <c r="J62" s="18"/>
       <c r="K62" s="17"/>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A63" s="47"/>
-      <c r="B63" s="54" t="str">
+      <c r="A63" s="16"/>
+      <c r="B63" s="32" t="str">
         <f>B50</f>
         <v>-for plinth level</v>
       </c>
-      <c r="C63" s="55">
+      <c r="C63" s="17">
         <f>C50</f>
         <v>4</v>
       </c>
-      <c r="D63" s="53">
+      <c r="D63" s="33">
         <f>D50</f>
         <v>3.2764401097226452</v>
       </c>
-      <c r="E63" s="55">
+      <c r="E63" s="17">
         <f>E50</f>
         <v>0.45</v>
       </c>
-      <c r="F63" s="55">
+      <c r="F63" s="17">
         <v>0.05</v>
       </c>
-      <c r="G63" s="53">
+      <c r="G63" s="33">
         <f t="shared" si="19"/>
         <v>0.29487960987503808</v>
       </c>
-      <c r="H63" s="55"/>
-      <c r="I63" s="55"/>
-      <c r="J63" s="56"/>
+      <c r="H63" s="17"/>
+      <c r="I63" s="17"/>
+      <c r="J63" s="18"/>
       <c r="K63" s="17"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64" s="47"/>
-      <c r="B64" s="54"/>
-      <c r="C64" s="55">
+      <c r="A64" s="16"/>
+      <c r="B64" s="32"/>
+      <c r="C64" s="17">
         <v>1</v>
       </c>
-      <c r="D64" s="53">
+      <c r="D64" s="33">
         <f>13.75/3.281</f>
         <v>4.190795489180128</v>
       </c>
-      <c r="E64" s="53">
+      <c r="E64" s="33">
         <f>13.75/3.281</f>
         <v>4.190795489180128</v>
       </c>
-      <c r="F64" s="53">
+      <c r="F64" s="33">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="G64" s="53">
+      <c r="G64" s="33">
         <f t="shared" si="19"/>
         <v>1.3172075124099381</v>
       </c>
-      <c r="H64" s="55"/>
-      <c r="I64" s="55"/>
-      <c r="J64" s="56"/>
+      <c r="H64" s="17"/>
+      <c r="I64" s="17"/>
+      <c r="J64" s="18"/>
       <c r="K64" s="17"/>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A65" s="47"/>
-      <c r="B65" s="54" t="s">
-        <v>71</v>
-      </c>
-      <c r="C65" s="55">
+      <c r="A65" s="16"/>
+      <c r="B65" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="C65" s="17">
         <v>-1</v>
       </c>
-      <c r="D65" s="53">
+      <c r="D65" s="33">
         <v>1.5</v>
       </c>
-      <c r="E65" s="53">
+      <c r="E65" s="33">
         <v>1.8</v>
       </c>
-      <c r="F65" s="53">
+      <c r="F65" s="33">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="G65" s="53">
+      <c r="G65" s="33">
         <f t="shared" si="19"/>
         <v>-0.20250000000000001</v>
       </c>
-      <c r="H65" s="55"/>
-      <c r="I65" s="55"/>
-      <c r="J65" s="56"/>
+      <c r="H65" s="17"/>
+      <c r="I65" s="17"/>
+      <c r="J65" s="18"/>
       <c r="K65" s="17"/>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A66" s="47"/>
-      <c r="B66" s="54" t="str">
+      <c r="A66" s="16"/>
+      <c r="B66" s="32" t="str">
         <f>B53</f>
         <v>-for railing</v>
       </c>
-      <c r="C66" s="55">
+      <c r="C66" s="17">
         <f>C53</f>
         <v>6</v>
       </c>
-      <c r="D66" s="53">
+      <c r="D66" s="33">
         <f>D53</f>
         <v>0.3</v>
       </c>
-      <c r="E66" s="53">
+      <c r="E66" s="33">
         <f>E53</f>
         <v>0.3</v>
       </c>
-      <c r="F66" s="53">
+      <c r="F66" s="33">
         <v>0.45</v>
       </c>
-      <c r="G66" s="53">
+      <c r="G66" s="33">
         <f t="shared" si="19"/>
         <v>0.24299999999999997</v>
       </c>
-      <c r="H66" s="55"/>
-      <c r="I66" s="55"/>
-      <c r="J66" s="56"/>
+      <c r="H66" s="17"/>
+      <c r="I66" s="17"/>
+      <c r="J66" s="18"/>
       <c r="K66" s="17"/>
     </row>
-    <row r="67" spans="1:16" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="39"/>
-      <c r="B67" s="48" t="s">
-        <v>42</v>
-      </c>
-      <c r="C67" s="41"/>
-      <c r="D67" s="51"/>
-      <c r="E67" s="52"/>
-      <c r="F67" s="52"/>
-      <c r="G67" s="46">
+    <row r="67" spans="1:16" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="2"/>
+      <c r="B67" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="C67" s="3"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="5"/>
+      <c r="F67" s="5"/>
+      <c r="G67" s="42">
         <f>SUM(G58:G66)</f>
         <v>3.4883371222849764</v>
       </c>
-      <c r="H67" s="44" t="s">
-        <v>67</v>
-      </c>
-      <c r="I67" s="45">
+      <c r="H67" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I67" s="6">
         <v>10964.46</v>
       </c>
-      <c r="J67" s="46">
+      <c r="J67" s="42">
         <f>G67*I67</f>
         <v>38247.732843808728</v>
       </c>
       <c r="K67" s="5"/>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A68" s="47"/>
-      <c r="B68" s="54" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="55"/>
-      <c r="D68" s="55"/>
-      <c r="E68" s="55"/>
-      <c r="F68" s="55"/>
-      <c r="G68" s="55"/>
-      <c r="H68" s="55"/>
-      <c r="I68" s="55"/>
-      <c r="J68" s="56">
+      <c r="A68" s="16"/>
+      <c r="B68" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="C68" s="17"/>
+      <c r="D68" s="17"/>
+      <c r="E68" s="17"/>
+      <c r="F68" s="17"/>
+      <c r="G68" s="17"/>
+      <c r="H68" s="17"/>
+      <c r="I68" s="17"/>
+      <c r="J68" s="18">
         <f>0.13*G67*53818.03/15</f>
         <v>1627.0404097761368</v>
       </c>
       <c r="K68" s="17"/>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A69" s="47"/>
-      <c r="B69" s="54" t="s">
-        <v>32</v>
-      </c>
-      <c r="C69" s="55"/>
-      <c r="D69" s="55"/>
-      <c r="E69" s="55"/>
-      <c r="F69" s="55"/>
-      <c r="G69" s="55"/>
-      <c r="H69" s="55"/>
-      <c r="I69" s="55"/>
-      <c r="J69" s="56">
+      <c r="A69" s="16"/>
+      <c r="B69" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="C69" s="17"/>
+      <c r="D69" s="17"/>
+      <c r="E69" s="17"/>
+      <c r="F69" s="17"/>
+      <c r="G69" s="17"/>
+      <c r="H69" s="17"/>
+      <c r="I69" s="17"/>
+      <c r="J69" s="18">
         <f>0.13*G67*21432.6/15</f>
         <v>647.95582979473659</v>
       </c>
       <c r="K69" s="17"/>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A70" s="47"/>
-      <c r="B70" s="54" t="s">
-        <v>33</v>
-      </c>
-      <c r="C70" s="55"/>
-      <c r="D70" s="55"/>
-      <c r="E70" s="55"/>
-      <c r="F70" s="55"/>
-      <c r="G70" s="55"/>
-      <c r="H70" s="55"/>
-      <c r="I70" s="55"/>
-      <c r="J70" s="56">
-        <f>0.13*G67*(25719.12+13573.98+4286.52/15)</f>
-        <v>17948.376485314202</v>
+      <c r="A70" s="16"/>
+      <c r="B70" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="C70" s="17"/>
+      <c r="D70" s="17"/>
+      <c r="E70" s="17"/>
+      <c r="F70" s="17"/>
+      <c r="G70" s="17"/>
+      <c r="H70" s="17"/>
+      <c r="I70" s="17"/>
+      <c r="J70" s="18">
+        <f>0.13*G67*(25719.12+13573.98+4286.52)/15</f>
+        <v>1317.5101872492974</v>
       </c>
       <c r="K70" s="17"/>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A71" s="47"/>
-      <c r="B71" s="54" t="s">
-        <v>68</v>
-      </c>
-      <c r="C71" s="55"/>
-      <c r="D71" s="55"/>
-      <c r="E71" s="55"/>
-      <c r="F71" s="55"/>
-      <c r="G71" s="55"/>
-      <c r="H71" s="55"/>
-      <c r="I71" s="55"/>
-      <c r="J71" s="56">
+      <c r="A71" s="16"/>
+      <c r="B71" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="C71" s="17"/>
+      <c r="D71" s="17"/>
+      <c r="E71" s="17"/>
+      <c r="F71" s="17"/>
+      <c r="G71" s="17"/>
+      <c r="H71" s="17"/>
+      <c r="I71" s="17"/>
+      <c r="J71" s="18">
         <f>0.13*G67*(6325.7/15)</f>
         <v>191.24017583179665</v>
       </c>
@@ -2891,7 +2850,7 @@
     <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72" s="16"/>
       <c r="B72" s="32" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C72" s="17"/>
       <c r="D72" s="17"/>
@@ -2907,24 +2866,24 @@
       <c r="K72" s="17"/>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A73" s="47"/>
-      <c r="B73" s="54"/>
-      <c r="C73" s="55"/>
-      <c r="D73" s="55"/>
-      <c r="E73" s="55"/>
-      <c r="F73" s="55"/>
-      <c r="G73" s="55"/>
-      <c r="H73" s="55"/>
-      <c r="I73" s="55"/>
-      <c r="J73" s="56"/>
+      <c r="A73" s="16"/>
+      <c r="B73" s="32"/>
+      <c r="C73" s="17"/>
+      <c r="D73" s="17"/>
+      <c r="E73" s="17"/>
+      <c r="F73" s="17"/>
+      <c r="G73" s="17"/>
+      <c r="H73" s="17"/>
+      <c r="I73" s="17"/>
+      <c r="J73" s="18"/>
       <c r="K73" s="17"/>
     </row>
     <row r="74" spans="1:16" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A74" s="16">
         <v>6</v>
       </c>
-      <c r="B74" s="35" t="s">
-        <v>34</v>
+      <c r="B74" s="46" t="s">
+        <v>31</v>
       </c>
       <c r="C74" s="17"/>
       <c r="D74" s="17"/>
@@ -2938,8 +2897,8 @@
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" s="16"/>
-      <c r="B75" s="54" t="s">
-        <v>65</v>
+      <c r="B75" s="32" t="s">
+        <v>61</v>
       </c>
       <c r="C75" s="17">
         <v>1</v>
@@ -3000,10 +2959,10 @@
       <c r="I76" s="17"/>
       <c r="J76" s="17"/>
       <c r="K76" s="17"/>
-      <c r="M76" s="36"/>
-      <c r="N76" s="36"/>
-      <c r="O76" s="36"/>
-      <c r="P76" s="36"/>
+      <c r="M76" s="35"/>
+      <c r="N76" s="35"/>
+      <c r="O76" s="35"/>
+      <c r="P76" s="35"/>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77" s="16"/>
@@ -3034,15 +2993,15 @@
       <c r="I77" s="17"/>
       <c r="J77" s="17"/>
       <c r="K77" s="17"/>
-      <c r="M77" s="36"/>
-      <c r="N77" s="36"/>
-      <c r="O77" s="36"/>
-      <c r="P77" s="36"/>
+      <c r="M77" s="35"/>
+      <c r="N77" s="35"/>
+      <c r="O77" s="35"/>
+      <c r="P77" s="35"/>
     </row>
     <row r="78" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2"/>
       <c r="B78" s="34" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C78" s="3"/>
       <c r="D78" s="4"/>
@@ -3053,7 +3012,7 @@
         <v>52.438555318500462</v>
       </c>
       <c r="H78" s="7" t="s">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="I78" s="6">
         <v>8987.83</v>
@@ -3067,7 +3026,7 @@
     <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79" s="16"/>
       <c r="B79" s="32" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C79" s="17"/>
       <c r="D79" s="17"/>
@@ -3085,7 +3044,7 @@
     <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A80" s="16"/>
       <c r="B80" s="32" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C80" s="17"/>
       <c r="D80" s="17"/>
@@ -3100,10 +3059,10 @@
       </c>
       <c r="K80" s="17"/>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="16"/>
       <c r="B81" s="32" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C81" s="17"/>
       <c r="D81" s="17"/>
@@ -3118,10 +3077,10 @@
       </c>
       <c r="K81" s="17"/>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="16"/>
       <c r="B82" s="32" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C82" s="17"/>
       <c r="D82" s="17"/>
@@ -3136,7 +3095,7 @@
       </c>
       <c r="K82" s="17"/>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="16"/>
       <c r="B83" s="32"/>
       <c r="C83" s="17"/>
@@ -3149,12 +3108,12 @@
       <c r="J83" s="18"/>
       <c r="K83" s="17"/>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="16">
         <v>7</v>
       </c>
-      <c r="B84" s="40" t="s">
-        <v>72</v>
+      <c r="B84" s="39" t="s">
+        <v>68</v>
       </c>
       <c r="C84" s="17"/>
       <c r="D84" s="17"/>
@@ -3166,10 +3125,10 @@
       <c r="J84" s="18"/>
       <c r="K84" s="17"/>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="16"/>
       <c r="B85" s="32" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C85" s="17">
         <v>1</v>
@@ -3191,21 +3150,21 @@
       <c r="J85" s="18"/>
       <c r="K85" s="17"/>
     </row>
-    <row r="86" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
       <c r="B86" s="34" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C86" s="3"/>
       <c r="D86" s="4"/>
       <c r="E86" s="5"/>
       <c r="F86" s="5"/>
       <c r="G86" s="6">
-        <f>SUM(G83:G85)</f>
+        <f>SUM(G85)</f>
         <v>2.4000000000000004</v>
       </c>
       <c r="H86" s="7" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="I86" s="6">
         <v>1017.47</v>
@@ -3216,10 +3175,10 @@
       </c>
       <c r="K86" s="5"/>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="16"/>
       <c r="B87" s="32" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="C87" s="17"/>
       <c r="D87" s="17"/>
@@ -3234,7 +3193,7 @@
       </c>
       <c r="K87" s="17"/>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="16"/>
       <c r="B88" s="17"/>
       <c r="C88" s="17"/>
@@ -3247,163 +3206,269 @@
       <c r="J88" s="17"/>
       <c r="K88" s="17"/>
     </row>
-    <row r="89" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="2">
+    <row r="89" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A89" s="16">
         <v>8</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="B89" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="C89" s="17"/>
+      <c r="D89" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="E89" s="38" t="s">
+        <v>75</v>
+      </c>
+      <c r="F89" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="G89" s="17"/>
+      <c r="H89" s="17"/>
+      <c r="I89" s="17"/>
+      <c r="J89" s="18"/>
+      <c r="K89" s="17"/>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A90" s="16"/>
+      <c r="B90" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="C90" s="17">
+        <v>1</v>
+      </c>
+      <c r="D90" s="17">
+        <v>185</v>
+      </c>
+      <c r="E90" s="17">
+        <v>0.13500000000000001</v>
+      </c>
+      <c r="F90" s="17">
+        <f>C90*D90*E90</f>
+        <v>24.975000000000001</v>
+      </c>
+      <c r="G90" s="33">
+        <f>F90</f>
+        <v>24.975000000000001</v>
+      </c>
+      <c r="H90" s="17"/>
+      <c r="I90" s="17"/>
+      <c r="J90" s="18"/>
+      <c r="K90" s="17"/>
+    </row>
+    <row r="91" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="2"/>
+      <c r="B91" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" s="3"/>
+      <c r="D91" s="4"/>
+      <c r="E91" s="5"/>
+      <c r="F91" s="5"/>
+      <c r="G91" s="6">
+        <f>SUM(G90)</f>
+        <v>24.975000000000001</v>
+      </c>
+      <c r="H91" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I91" s="6">
+        <v>287</v>
+      </c>
+      <c r="J91" s="18">
+        <f>G91*I91</f>
+        <v>7167.8250000000007</v>
+      </c>
+      <c r="K91" s="5"/>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A92" s="16"/>
+      <c r="B92" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C92" s="17"/>
+      <c r="D92" s="17"/>
+      <c r="E92" s="17"/>
+      <c r="F92" s="17"/>
+      <c r="G92" s="17"/>
+      <c r="H92" s="17"/>
+      <c r="I92" s="17"/>
+      <c r="J92" s="18">
+        <f>0.13*J91</f>
+        <v>931.81725000000017</v>
+      </c>
+      <c r="K92" s="17"/>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A93" s="16"/>
+      <c r="B93" s="17"/>
+      <c r="C93" s="17"/>
+      <c r="D93" s="17"/>
+      <c r="E93" s="17"/>
+      <c r="F93" s="17"/>
+      <c r="G93" s="17"/>
+      <c r="H93" s="17"/>
+      <c r="I93" s="17"/>
+      <c r="J93" s="17"/>
+      <c r="K93" s="17"/>
+    </row>
+    <row r="94" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="2">
+        <v>9</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C94" s="3">
+        <v>1</v>
+      </c>
+      <c r="D94" s="4"/>
+      <c r="E94" s="5"/>
+      <c r="F94" s="5"/>
+      <c r="G94" s="7">
+        <f t="shared" ref="G94" si="20">PRODUCT(C94:F94)</f>
+        <v>1</v>
+      </c>
+      <c r="H94" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I94" s="6">
+        <v>500</v>
+      </c>
+      <c r="J94" s="7">
+        <f>G94*I94</f>
+        <v>500</v>
+      </c>
+      <c r="K94" s="5"/>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A95" s="2"/>
+      <c r="B95" s="8"/>
+      <c r="C95" s="3"/>
+      <c r="D95" s="4"/>
+      <c r="E95" s="5"/>
+      <c r="F95" s="5"/>
+      <c r="G95" s="6"/>
+      <c r="H95" s="7"/>
+      <c r="I95" s="6"/>
+      <c r="J95" s="18"/>
+      <c r="K95" s="5"/>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A96" s="21"/>
+      <c r="B96" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C96" s="23"/>
+      <c r="D96" s="24"/>
+      <c r="E96" s="24"/>
+      <c r="F96" s="24"/>
+      <c r="G96" s="18"/>
+      <c r="H96" s="18"/>
+      <c r="I96" s="18"/>
+      <c r="J96" s="18">
+        <f>SUM(J9:J94)</f>
+        <v>786973.54597297299</v>
+      </c>
+      <c r="K96" s="25"/>
+    </row>
+    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="M97" s="20"/>
+      <c r="N97" s="20"/>
+      <c r="O97" s="20"/>
+      <c r="P97" s="20"/>
+      <c r="Q97" s="20"/>
+      <c r="R97" s="20"/>
+      <c r="S97" s="20"/>
+    </row>
+    <row r="98" spans="1:19" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="26"/>
+      <c r="B98" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C89" s="3">
-        <v>1</v>
-      </c>
-      <c r="D89" s="4"/>
-      <c r="E89" s="5"/>
-      <c r="F89" s="5"/>
-      <c r="G89" s="7">
-        <f t="shared" ref="G89" si="20">PRODUCT(C89:F89)</f>
-        <v>1</v>
-      </c>
-      <c r="H89" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I89" s="6">
-        <v>500</v>
-      </c>
-      <c r="J89" s="7">
-        <f>G89*I89</f>
-        <v>500</v>
-      </c>
-      <c r="K89" s="5"/>
-    </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A90" s="2"/>
-      <c r="B90" s="8"/>
-      <c r="C90" s="3"/>
-      <c r="D90" s="4"/>
-      <c r="E90" s="5"/>
-      <c r="F90" s="5"/>
-      <c r="G90" s="6"/>
-      <c r="H90" s="7"/>
-      <c r="I90" s="6"/>
-      <c r="J90" s="18"/>
-      <c r="K90" s="5"/>
-    </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A91" s="21"/>
-      <c r="B91" s="22" t="s">
+      <c r="C98" s="47">
+        <f>J96</f>
+        <v>786973.54597297299</v>
+      </c>
+      <c r="D98" s="48"/>
+      <c r="E98" s="9">
+        <v>100</v>
+      </c>
+      <c r="F98" s="26"/>
+      <c r="G98" s="28"/>
+      <c r="H98" s="26"/>
+      <c r="I98" s="29"/>
+      <c r="J98" s="30"/>
+      <c r="K98" s="31"/>
+      <c r="M98" s="19"/>
+      <c r="N98" s="19"/>
+      <c r="O98" s="19"/>
+      <c r="P98" s="19"/>
+      <c r="Q98" s="19"/>
+      <c r="R98" s="19"/>
+      <c r="S98" s="19"/>
+    </row>
+    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B99" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C99" s="51">
+        <v>700000</v>
+      </c>
+      <c r="D99" s="52"/>
+      <c r="E99" s="9"/>
+    </row>
+    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B100" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C91" s="23"/>
-      <c r="D91" s="24"/>
-      <c r="E91" s="24"/>
-      <c r="F91" s="24"/>
-      <c r="G91" s="18"/>
-      <c r="H91" s="18"/>
-      <c r="I91" s="18"/>
-      <c r="J91" s="18">
-        <f>SUM(J9:J89)</f>
-        <v>795504.77002103801</v>
-      </c>
-      <c r="K91" s="25"/>
-    </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="M92" s="20"/>
-      <c r="N92" s="20"/>
-      <c r="O92" s="20"/>
-      <c r="P92" s="20"/>
-      <c r="Q92" s="20"/>
-      <c r="R92" s="20"/>
-      <c r="S92" s="20"/>
-    </row>
-    <row r="93" spans="1:19" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="26"/>
-      <c r="B93" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="C93" s="57">
-        <f>J91</f>
-        <v>795504.77002103801</v>
-      </c>
-      <c r="D93" s="58"/>
-      <c r="E93" s="9">
-        <v>100</v>
-      </c>
-      <c r="F93" s="26"/>
-      <c r="G93" s="28"/>
-      <c r="H93" s="26"/>
-      <c r="I93" s="29"/>
-      <c r="J93" s="30"/>
-      <c r="K93" s="31"/>
-      <c r="M93" s="19"/>
-      <c r="N93" s="19"/>
-      <c r="O93" s="19"/>
-      <c r="P93" s="19"/>
-      <c r="Q93" s="19"/>
-      <c r="R93" s="19"/>
-      <c r="S93" s="19"/>
-    </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B94" s="27" t="s">
+      <c r="C100" s="51">
+        <f>C99-C102-C103</f>
+        <v>665000</v>
+      </c>
+      <c r="D100" s="52"/>
+      <c r="E100" s="9">
+        <f>C100/C98*100</f>
+        <v>84.500934421858958</v>
+      </c>
+    </row>
+    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B101" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="C101" s="53">
+        <f>C98-C100</f>
+        <v>121973.54597297299</v>
+      </c>
+      <c r="D101" s="53"/>
+      <c r="E101" s="9">
+        <f>100-E100</f>
+        <v>15.499065578141042</v>
+      </c>
+    </row>
+    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B102" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C102" s="47">
+        <f>C99*0.03</f>
+        <v>21000</v>
+      </c>
+      <c r="D102" s="48"/>
+      <c r="E102" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B103" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C94" s="61">
-        <v>700000</v>
-      </c>
-      <c r="D94" s="62"/>
-      <c r="E94" s="9"/>
-    </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B95" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="C95" s="61">
-        <f>C94-C97-C98</f>
-        <v>665000</v>
-      </c>
-      <c r="D95" s="62"/>
-      <c r="E95" s="9">
-        <f>C95/C93*100</f>
-        <v>83.594721874818347</v>
-      </c>
-    </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B96" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="C96" s="63">
-        <f>C93-C95</f>
-        <v>130504.77002103801</v>
-      </c>
-      <c r="D96" s="63"/>
-      <c r="E96" s="9">
-        <f>100-E95</f>
-        <v>16.405278125181653</v>
-      </c>
-    </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B97" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="C97" s="57">
-        <f>C94*0.03</f>
-        <v>21000</v>
-      </c>
-      <c r="D97" s="58"/>
-      <c r="E97" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B98" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="C98" s="57">
-        <f>C94*0.02</f>
+      <c r="C103" s="47">
+        <f>C99*0.02</f>
         <v>14000</v>
       </c>
-      <c r="D98" s="58"/>
-      <c r="E98" s="9">
+      <c r="D103" s="48"/>
+      <c r="E103" s="9">
         <v>2</v>
       </c>
     </row>
@@ -3416,17 +3481,17 @@
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A5:K5"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="C103:D103"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="H7:K7"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
   </mergeCells>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
-  <pageSetup paperSize="9" scale="90" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="80" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;LPrepared By:&amp;CChecked By:&amp;RApproved By:</oddFooter>
   </headerFooter>
